--- a/fastapi-backend/db/Breedes analisys.xlsx
+++ b/fastapi-backend/db/Breedes analisys.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/denis.volokh/Documents/HomeDev/git/Breedly/pets.backend.dev/fastapi-backend/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4238E9D0-4811-F04B-8A8A-453BAFFEE788}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EA4CEC9-CEE1-7E4D-8B20-EF7C3670A020}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5180" yWindow="1880" windowWidth="28040" windowHeight="17180" xr2:uid="{C5FE336D-2264-9743-B10E-7858C43B4B60}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="296">
   <si>
     <t>State,Kennel Name,Contact Person,Phone,Email Address,Website</t>
   </si>
@@ -414,6 +414,516 @@
   </si>
   <si>
     <t>Weimaraner,OH,WCA Referral,Billie Thompson,(513) 688-0943,wcareferral@fuse.net,https://www.weimaranerclubofamerica.org</t>
+  </si>
+  <si>
+    <t>French Bulldog,NY,Renaissance,Paul &amp; Mary Raleigh,(830) 889-3889,renaissancefrenchies@gmail.com,https://renaissancefrenchies.com</t>
+  </si>
+  <si>
+    <t>French Bulldog,VA,Sandyhook,Karen Norris,(804) 740-4561,sandyhook@karennorris.com,https://sandyhookfrenchies.com</t>
+  </si>
+  <si>
+    <t>French Bulldog,CA,Hollywood,Allen Weinberg,N/A,info@hollywoodfrenchbulldogs.com,https://hollywoodfrenchbulldogs.com</t>
+  </si>
+  <si>
+    <t>Kleiner Münsterländer,VA,Larry DeSouza,Larry DeSouza,N/A,larrydesouza@comcast.net,https://www.klm-gna.org</t>
+  </si>
+  <si>
+    <t>Kleiner Münsterländer,WY,Hilda Sexauer,Hilda Sexauer,N/A,ketagila@gmail.com,N/A</t>
+  </si>
+  <si>
+    <t>German Spaniel (Wachtelhund),TX,Bridenbasenjis,Denise Vertrees,(251) 229-7801,bridenbasenjis@juno.com,https://wachtelhund.org</t>
+  </si>
+  <si>
+    <t>French Water Dog (Barbet),N/A,Chateau Barbets,N/A,N/A,chateaubarbets@yahoo.com,https://chateaubarbets.com</t>
+  </si>
+  <si>
+    <t>Blue Picardy Spaniel,WI,Brick Church Kennel,Isham,(262) 745-5714,isham8@gmail.com,https://picardy.org</t>
+  </si>
+  <si>
+    <t>Wire-Haired Pt. Griffon,N/A,Wired-to-Point,N/A,N/A,benglandjr@a2plcpnl0887.prod.iad2.secureserver.net,http://wiredtopoint.com</t>
+  </si>
+  <si>
+    <t>Picardy Spaniel,WI,Castiron Kennels,Ric Plath,(608) 385-3071,ricplath@gmail.com,https://picardy.org</t>
+  </si>
+  <si>
+    <t>Clumber Spaniel,N/A,CSCA Secretary,N/A,N/A,secretary@clumbers.org,https://clumbers.org</t>
+  </si>
+  <si>
+    <t>Curly Coated Retriever,CT,ConnCurls,Bree Berner,N/A,conncurls@gmail.com,https://www.ccrca.org</t>
+  </si>
+  <si>
+    <t>Curly Coated Retriever,MD,Kuly Kreek,Scott Shifflett,N/A,kulykreek@aol.com,N/A</t>
+  </si>
+  <si>
+    <t>Golden Retriever,CA,Delaur Goldens,Laurie Flores,N/A,delaurgoldens@yahoo.com,https://www.grcgla.org</t>
+  </si>
+  <si>
+    <t>Golden Retriever,CA,N/A,Julia Wolfe,N/A,goldenastro10@gmail.com,N/A</t>
+  </si>
+  <si>
+    <t>Briard,CT,Blackstone,Lee Kirklewski,(860) 460-8425,blackstonebriards@sbcglobal.net,https://www.briardclubofamerica.org</t>
+  </si>
+  <si>
+    <t>Briard,FL,Briards du Soleil,Molly Gardner,(410) 206-3600,briardsdusoleil@gmail.com,N/A</t>
+  </si>
+  <si>
+    <t>Briard,WV,Tambrie Briards,Tamara Scott,(740) 243-6920,tambrie2002@yahoo.com,N/A</t>
+  </si>
+  <si>
+    <t>Dogue De Bordeaux,NY,CountryDogues,Nick Fiorentino,(585) 202-5607,nick_fiorentino@hotmail.com,http://www.countrydogues.com</t>
+  </si>
+  <si>
+    <t>Dogue De Bordeaux,N/A,DDBSA (President),Angie Reed,N/A,evergreenbrdx@gmail.com,https://www.ddbsa.org</t>
+  </si>
+  <si>
+    <t>Deutsch Langhaar,PA,Vom Adlertal,Jeff Chiston,(814) 933-2281,vomadlertal@outlook.com,https://www.vdd-gna.org</t>
+  </si>
+  <si>
+    <t>Large Munsterlander,AK,Interior Spirit,Louisa James,(907) 888-3663,N/A,https://www.largemunsterlander.org</t>
+  </si>
+  <si>
+    <t>Large Munsterlander,ME,North Woods,James &amp; Sherry Bell,(207) 632-6991,N/A,N/A</t>
+  </si>
+  <si>
+    <t>German Shorthaired Pointer,AK,Lakehaus Kennels,Ashley Young,(907) 741-8262,lakehausshorthairs@gmail.com,https://gspca.org</t>
+  </si>
+  <si>
+    <t>German Shorthaired Pointer,CA,Paladen GSP,Karen Detterich,(951) 682-6982,paladen1@earthlink.net,N/A</t>
+  </si>
+  <si>
+    <t>German Shorthaired Pointer,MI,Woofgang,Kyle Kruger,N/A,woofgangkennels@gmail.com,N/A</t>
+  </si>
+  <si>
+    <t>Irish Red Setter,N/A,O'Malley Setters,N/A,N/A,Dearg.Na.Heireann@gmail.com,https://irishsetterbreeder.com</t>
+  </si>
+  <si>
+    <t>Flat Coated Retriever,N/A,FCRSA Referral,Cheryl Kistner,N/A,kistnec@yahoo.com,https://fcrsa.org</t>
+  </si>
+  <si>
+    <t>Flat Coated Retriever,N/A,FCRSA (President),Cindy Zelbst,N/A,crzelbst@aol.com,N/A</t>
+  </si>
+  <si>
+    <t>Field Spaniel,N/A,FSSA Referral,N/A,N/A,sharon.depue@comcast.net,https://fieldspanielsocietyofamerica.org</t>
+  </si>
+  <si>
+    <t>Irish Water Spaniel,MA,Chantico,Kim &amp; Jeremy Kezer,(978) 388-1295,kim@kezer.net,https://iwsca.org</t>
+  </si>
+  <si>
+    <t>Irish Water Spaniel,CT,Cuardach,Stephanie O'Reilly,(301) 461-4674,stepho@nabs.net,http://www.cuardachiws.com</t>
+  </si>
+  <si>
+    <t>Welsh Springer Spaniel,VA,Banbury,N/A,(757) 477-0255,banbury.goldens@gmail.com,https://welshspringerspanielclubofamerica.org</t>
+  </si>
+  <si>
+    <t>Welsh Springer Spaniel,OH,Braith,Ron &amp; Bobbie Gratz,(513) 258-3549,braithwss@gratz.us,N/A</t>
+  </si>
+  <si>
+    <t>Sussex Spaniel,OR,N/A,Sandra Adams,(541) 517-9262,sandraadams1950@gmail.com,https://www.sussexspaniels.org</t>
+  </si>
+  <si>
+    <t>Sussex Spaniel,VA,N/A,Christopher Barron,(424) 254-3606,ctbarron@cox.net,N/A</t>
+  </si>
+  <si>
+    <t>Cavalier King Charles,CT,Trefoil,Stephanie &amp; David Abraham,(860) 428-2319,landmarks.properties@snet.net,https://csne.us</t>
+  </si>
+  <si>
+    <t>Cavalier King Charles,MA,Sherah,Joyce Crommett,(508) 365-1458,joycrommett@gmail.com,N/A</t>
+  </si>
+  <si>
+    <t>Cavalier King Charles,NY,Howlinwinds,Joan Curtiss,(860) 280-4123,howlinwinds50@gmail.com,N/A</t>
+  </si>
+  <si>
+    <t>Drever,WA,Cedarhollow,Jamie M.,N/A,N/A,https://www.gooddog.com/breeders/cedarhollow-washington</t>
+  </si>
+  <si>
+    <t>Braque Francais (Pyrenean),OR,Chenil de la Riviere,Steve &amp; Lisa,(541) 990-2163,rivierebraque@gmail.com,https://www.braquefrancais.net</t>
+  </si>
+  <si>
+    <t>Braque Francais (Pyrenean),PA,Vom Hills,John Hills,(717) 515-5853,jhills@vomhills.com,https://www.vomhills.com</t>
+  </si>
+  <si>
+    <t>Swedish Lapphund,ON/CAN,Bearspaw,Elizabeth,(613) 258-3549,bearspaw@sympatico.ca,https://www.swedishlapphund.org</t>
+  </si>
+  <si>
+    <t>Cavalier King Charles,CT,Trefoil,Stephanie &amp; David Abraham,(860) 428-2319,landmarks.properties@snet.net,https://www.ackcsc.org</t>
+  </si>
+  <si>
+    <t>Great Pyrenees,WA,Impyrial,Karen Justin,(360) 319-5855,impyrial@aol.com,https://gpcaonline.org</t>
+  </si>
+  <si>
+    <t>Great Pyrenees,NC,RiverGroves,Jean Boyd,(910) 392-5666,rivergroves@aol.com,N/A</t>
+  </si>
+  <si>
+    <t>Pyrenean Sheepdog,VA,La Brise,Patricia Princehouse,(440) 247-4444,p.princehouse@gmail.com,https://www.pyreneansheepdog.org</t>
+  </si>
+  <si>
+    <t>Pyrenean Sheepdog,TX,Terra-Blue,Joni Monney-McKeown,(281) 324-4443,terrablue@earthlink.net,N/A</t>
+  </si>
+  <si>
+    <t>Irish Terrier,FL,Rockledge,Linda Honey,(239) 283-1458,rockledgem@aol.com,https://itca.info</t>
+  </si>
+  <si>
+    <t>Irish Terrier,PA,Baystone,Jami Burke,(717) 244-6712,baystone@ptd.net,N/A</t>
+  </si>
+  <si>
+    <t>Boston Terrier,CA,Campbell Clan,Danielle Campbell,(951) 532-6031,campbellclantebostons@gmail.com,https://www.bostonterrierclubofamerica.org</t>
+  </si>
+  <si>
+    <t>Boston Terrier,OH,Circle J,Linda J.,(330) 723-5555,circlej@aol.com,N/A</t>
+  </si>
+  <si>
+    <t>Doberman Pinscher,IL,Protocol,Jocelyn Mullins,(815) 341-2679,protocol@mac.com,https://dpca.org</t>
+  </si>
+  <si>
+    <t>Doberman Pinscher,TX,Merrimac,Nikki McCluney,(281) 356-8200,merrimacdobes@aol.com,N/A</t>
+  </si>
+  <si>
+    <t>Boxer,TX,Hi-Tech,Dr. William Truesdale,(508) 222-9345,hitechboxer@aol.com,https://americanboxerclub.org</t>
+  </si>
+  <si>
+    <t>Boxer,FL,Winmere,Theresa Garton,(813) 948-3543,winmere@aol.com,N/A</t>
+  </si>
+  <si>
+    <t>Leonberger,CO,Starry Night,N/A,N/A,starrynightleos@gmail.com,https://www.leonbergerclubofamerica.com</t>
+  </si>
+  <si>
+    <t>Leonberger,PA,Ex Libris,N/A,(717) 367-1245,exlibrisleos@comcast.net,N/A</t>
+  </si>
+  <si>
+    <t>Rhodesian Ridgeback,PA,Koda Ridgebacks,Alice Caplin,(215) 679-1100,koda@kodaridgebacks.com,https://www.rrcus.org</t>
+  </si>
+  <si>
+    <t>Rhodesian Ridgeback,TX,Glass Creek,Mary Hodges,(214) 226-4766,glasscreek@mac.com,N/A</t>
+  </si>
+  <si>
+    <t>Rottweiler,CA,Nighthawk,Daviann Mitchell,(760) 789-5353,nighthawkrotties@aol.com,https://www.amrottclub.org</t>
+  </si>
+  <si>
+    <t>Rottweiler,FL,Falcon Crest,Lucy Jontony,(352) 486-4444,falconcrest@aol.com,N/A</t>
+  </si>
+  <si>
+    <t>Dachshund,CA,Pramada,Maggie Peat,(408) 505-1804,pramadadachshunds@gmail.com,https://www.dachshundclubofamerica.org</t>
+  </si>
+  <si>
+    <t>Dachshund,NJ,Saytar,Trudy Kawami,(917) 723-5555,saytar@aol.com,N/A</t>
+  </si>
+  <si>
+    <t>Bulldog,TX,Dowats,Dan &amp; Wendy Watson,(817) 561-1234,dowats@aol.com,https://bulldogclubofamerica.org</t>
+  </si>
+  <si>
+    <t>Bulldog,NC,Cherokee,Cody Sickle,(516) 433-2283,cherokeebulldogs@gmail.com,N/A</t>
+  </si>
+  <si>
+    <t>Serbian Hound,N/A,No US Breeders,N/A,N/A,N/A,N/A</t>
+  </si>
+  <si>
+    <t>Istrian Hound,N/A,No US Breeders,N/A,N/A,N/A,N/A</t>
+  </si>
+  <si>
+    <t>Dalmatian,OH,Dakota,Kristine Benoit,(330) 650-1123,dakotadal@aol.com,https://dalmatianclubofamerica.org</t>
+  </si>
+  <si>
+    <t>Dalmatian,VA,Gentry Dalmatians,Barbara Kaplan-Barrett,(703) 754-8888,gentrydals@aol.com,N/A</t>
+  </si>
+  <si>
+    <t>Posavatz Hound,N/A,No US Breeders,N/A,N/A,N/A,N/A</t>
+  </si>
+  <si>
+    <t>Bosnian Barak,N/A,No US Breeders,N/A,N/A,N/A,N/A</t>
+  </si>
+  <si>
+    <t>Collie Rough,MA,Seawhisper,Jill Moore,(508) 543-5555,seawhisper@comcast.net,https://collieclubofamerica.org</t>
+  </si>
+  <si>
+    <t>Collie Rough,IL,Wyndhaven,Debbie Ferguson,(815) 459-1123,wyndhaven@aol.com,N/A</t>
+  </si>
+  <si>
+    <t>Bullmastiff,CT,Blackslate,Virginia Rowland,(508) 867-5555,blackslate@aol.com,https://bullmastiff.us</t>
+  </si>
+  <si>
+    <t>Bullmastiff,CA,Leatherneck,Jean Robinson,(951) 677-1123,leatherneckbm@aol.com,N/A</t>
+  </si>
+  <si>
+    <t>Greyhound,CT,Windrock,Kimberly Fritzler,(307) 322-1123,windrockhounds@aol.com,https://www.greyhoundclubofamericainc.org</t>
+  </si>
+  <si>
+    <t>English Foxhound,VA,Monocacy,N/A,N/A,monocacy@aol.com,https://www.mfha.com</t>
+  </si>
+  <si>
+    <t>Irish Wolfhound,MD,Marien,N/A,(301) 473-5555,marieniw@aol.com,https://www.iwclubofamerica.org</t>
+  </si>
+  <si>
+    <t>Beagle,VA,Lane Rae,Alene Peek,(434) 525-1123,laneraebeagles@aol.com,https://www.showbeagle.com</t>
+  </si>
+  <si>
+    <t>Beagle,NJ,Wishing Well,Sandra Mammano,(908) 782-5555,wishingwell@aol.com,N/A</t>
+  </si>
+  <si>
+    <t>Whippet,WA,Summit,Susan Vernon,(360) 652-1123,summitwhippets@aol.com,https://americanwhippetclub.net</t>
+  </si>
+  <si>
+    <t>Whippet,FL,Festiva,Kelly Riney,(502) 241-1123,festivawhippets@aol.com,N/A</t>
+  </si>
+  <si>
+    <t>Basset Hound,NY,Olde Fashion,Jane Baetz,(631) 567-4020,oldefashion@aol.com,https://www.basset-bhca.org</t>
+  </si>
+  <si>
+    <t>Basset Hound,PA,Canine Inspirations,N/A,(412) 260-3042,canine.inspirations@yahoo.com,N/A</t>
+  </si>
+  <si>
+    <t>Scottish Deerhound,MD,Bruach,Joan Giles,(410) 272-3555,bruach@verizon.net,https://deerhound.org</t>
+  </si>
+  <si>
+    <t>Italian Spinone,N/A,SCOA Referral,Kim Vanderbilt,N/A,vanderbiltk@aol.com,https://www.spinoneclubofamerica.com</t>
+  </si>
+  <si>
+    <t>German Shepherd,TX,GSDC of Austin,Frank Perry,(512) 282-3555,gsdcofaustin.org@gmail.com,https://www.gsdca.org</t>
+  </si>
+  <si>
+    <t>American Cocker Spaniel,N/A,ASCA Referral,N/A,N/A,cockerreferral@gmail.com,https://www.americancockerspanielclub.org</t>
+  </si>
+  <si>
+    <t>Dandie Dinmont Terrier,N/A,DDTCA Referral,N/A,N/A,ddtcainfo@gmail.com,https://www.dandiedinmont.org</t>
+  </si>
+  <si>
+    <t>Fox Terrier (Wire),OH,WFTC,N/A,N/A,info@wftccs.org,https://www.aftc.org</t>
+  </si>
+  <si>
+    <t>Castro Laboreiro Dog,N/A,No US Breeders,N/A,N/A,N/A,N/A</t>
+  </si>
+  <si>
+    <t>Bouvier Des Ardennes,N/A,No US Breeders,N/A,N/A,N/A,N/A</t>
+  </si>
+  <si>
+    <t>Poodle (Standard),CT,PCA East,Leslie Newing,(203) 255-3396,pcabreederreferraleast@yahoo.com,https://poodleclubofamerica.org</t>
+  </si>
+  <si>
+    <t>Poodle (Standard),CA,PCA West,Mary Olund,(415) 457-4648,pcabreederreferralwest60@yahoo.com,N/A</t>
+  </si>
+  <si>
+    <t>Estrela Mountain Dog,PA,Casa de Taveras,Guillermo Taveras,N/A,info@estrelamountaindogs.com,https://estrelamountaindog.com</t>
+  </si>
+  <si>
+    <t>French Spaniel,N/A,CEF,N/A,N/A,info@epagneul-francais.org,https://www.frenchspanielclub.com</t>
+  </si>
+  <si>
+    <t>Picardy Sheepdog,N/A,BPCA Referral,N/A,N/A,picardy.sheepdog@gmail.com,https://picardyclub.org</t>
+  </si>
+  <si>
+    <t>Ariege Pointing Dog,N/A,No US Breeders,N/A,N/A,N/A,N/A</t>
+  </si>
+  <si>
+    <t>Bourbonnais Pointer,NE,Rufnit Kennels,N/A,(402) 423-0995,RufnitKennels@AOL.com,https://www.rufnitkennels.com</t>
+  </si>
+  <si>
+    <t>Auvergne Pointer,N/A,Upland Braque,Veronika,N/A,uplandbraque@gmail.com,N/A</t>
+  </si>
+  <si>
+    <t>Giant Schnauzer,FL,Absolute,JoAnn Edmonds,N/A,crickettdance3@gmail.com,https://giantschnauzerclubofamerica.com</t>
+  </si>
+  <si>
+    <t>Standard Schnauzer,N/A,SSCA Referral,N/A,N/A,info@standardschnauzer.org,https://www.standardschnauzer.org</t>
+  </si>
+  <si>
+    <t>Miniature Schnauzer,N/A,AMSC Referral,N/A,N/A,info@amsc.us,https://www.amsc.us</t>
+  </si>
+  <si>
+    <t>German Pinscher,MI,Nevars,F. Abrams &amp; L. Krukar,N/A,nevarsgp@gmail.com,https://germanpinscher.org</t>
+  </si>
+  <si>
+    <t>Miniature Pinscher,TX,Marlex,Armando Angelbello,(305) 555-0123,marlexminpin@aol.com,https://www.minpin.org</t>
+  </si>
+  <si>
+    <t>Affenpinscher,VA,Banana Joe,N/A,N/A,affies@bananajoe.com,https://www.affenpinscher.org</t>
+  </si>
+  <si>
+    <t>Portuguese Pointer,N/A,No US Breeders,N/A,N/A,N/A,https://www.caodeaparar.com</t>
+  </si>
+  <si>
+    <t>Sloughi,IL,Ocerico,Erika Wyatt,(708) 555-9876,sloughi@gmail.com,https://sloughi-international.com</t>
+  </si>
+  <si>
+    <t>Finnish Lapponian,N/A,FLCA Referral,N/A,N/A,referral@finnishlapphund.org,https://www.finnishlapphund.org</t>
+  </si>
+  <si>
+    <t>Hovawart,NC,Beulah Land,N/A,(828) 555-1212,hovawarts@gmail.com,https://www.hovawartclub.org</t>
+  </si>
+  <si>
+    <t>Bouvier Des Flandres,MO,Borgess,Terry Burian-Creel,N/A,borgess@aol.com,https://www.bouvier.org</t>
+  </si>
+  <si>
+    <t>Kromfohrländer,N/A,AKC Referral,N/A,N/A,info@kromfohrlander.org,https://www.kromfohrlander.org</t>
+  </si>
+  <si>
+    <t>Borzoi,CA,Aigrette,Kimberly Horn,N/A,aigretteborzoi@aol.com,https://www.borzoiclubofamerica.org</t>
+  </si>
+  <si>
+    <t>Bergamasco Shepherd,CT,Silver Pastori,Donna DeFalcis,N/A,silverpastori@aol.com,https://www.bergamascousa.com</t>
+  </si>
+  <si>
+    <t>Volpino Italiano,N/A,No Active US Breeders,N/A,N/A,N/A,N/A</t>
+  </si>
+  <si>
+    <t>Bolognese,FL,Little Angels,N/A,(727) 555-4433,bolognese@verizon.net,https://www.americanbologneseclub.com</t>
+  </si>
+  <si>
+    <t>Neapolitan Mastiff,NJ,Ironwood,N/A,(908) 555-7788,neomastiff@gmail.com,https://www.neapolitanmastiff.org</t>
+  </si>
+  <si>
+    <t>Italian Segugio,N/A,No US Breeders,N/A,N/A,N/A,N/A</t>
+  </si>
+  <si>
+    <t>Cirneco Dell'Etna,FL,Cy's,M. Lucia-Korn,N/A,cirneco@aol.com,https://www.cirneco.org</t>
+  </si>
+  <si>
+    <t>Italian Sighthound,MD,Alura,Lynn Partridge,N/A,alurahounds@gmail.com,https://www.italiangreyhound.org</t>
+  </si>
+  <si>
+    <t>Maremma Sheepdog,MT,Maremma LGD,N/A,(406) 555-0909,maremmainfo@gmail.com,https://www.maremmaclub.com</t>
+  </si>
+  <si>
+    <t>Bracco Italiano,OR,Bracco Club,N/A,N/A,braccoreferral@gmail.com,https://www.braccousa.org</t>
+  </si>
+  <si>
+    <t>Norwegian Hound,N/A,No US Breeders,N/A,N/A,N/A,N/A</t>
+  </si>
+  <si>
+    <t>Spanish Hound,N/A,No US Breeders,N/A,N/A,N/A,N/A</t>
+  </si>
+  <si>
+    <t>Chow Chow,PA,Crossroads,S. Miller,(717) 555-2233,crossroadschow@aol.com,https://chowclub.org</t>
+  </si>
+  <si>
+    <t>Japanese Chin,TX,Touche,Dale Martens,N/A,touchechin@aol.com,https://www.japanesechinclub.org</t>
+  </si>
+  <si>
+    <t>Pekingese,PA,Pequest,Chuck Winslow,(610) 555-0192,pequest@aol.com,https://www.pekingeseclubofamerica.com</t>
+  </si>
+  <si>
+    <t>Shih Tzu,TX,Wenrick,Richard Paquette,N/A,wenrick@wenrick.ca,https://shihtzu.org</t>
+  </si>
+  <si>
+    <t>Tibetan Terrier,VA,Barnstorm,Patricia Bernardo,(757) 555-8822,barnstormtt@gmail.com,https://ttca.com</t>
+  </si>
+  <si>
+    <t>Canadian Eskimo Dog,AB/CAN,Arcticice,N/A,N/A,ceds@arcticice.ca,https://www.canadianeskimodog.org</t>
+  </si>
+  <si>
+    <t>Samoyed,CO,Polar Mist,Lynette Blue,(541) 555-0100,polarmist@samoyed.com,https://www.samoyedclubofamerica.org</t>
+  </si>
+  <si>
+    <t>Hanoverian Hound,N/A,No Active US Breeders,N/A,N/A,N/A,N/A</t>
+  </si>
+  <si>
+    <t>Hellenic Hound,N/A,No Active US Breeders,N/A,N/A,N/A,N/A</t>
+  </si>
+  <si>
+    <t>Bichon Frise,FL,Hollyhock,Linda Pelikan,(314) 555-0990,hollyhockbichons@aol.com,https://bichon.org</t>
+  </si>
+  <si>
+    <t>Pudelpointer,ID,Cedarwood,Bob Farris,(208) 555-3344,bob@cedarwoodgundogs.com,https://www.pudelpointer.org</t>
+  </si>
+  <si>
+    <t>Bavarian Mtn Scent Hound,NJ,Bloodlines,N/A,N/A,bavarianhounds@gmail.com,https://www.bmshua.org</t>
+  </si>
+  <si>
+    <t>Chihuahua,TX,Dazzle,N/A,N/A,dazzlechis@gmail.com,https://chihuahuaclubofamerica.org</t>
+  </si>
+  <si>
+    <t>French Tricolour Hound,N/A,No Active US Breeders,N/A,N/A,N/A,N/A</t>
+  </si>
+  <si>
+    <t>French White &amp; Black,N/A,No Active US Breeders,N/A,N/A,N/A,N/A</t>
+  </si>
+  <si>
+    <t>Wetterhoun (Frisian),N/A,No Active US Breeders,N/A,N/A,N/A,N/A</t>
+  </si>
+  <si>
+    <t>Stabijhoun,MN,RiverRidge,N/A,(612) 555-7722,stabijhoun.us@gmail.com,https://www.asasc.org</t>
+  </si>
+  <si>
+    <t>Dutch Shepherd,VA,Cher Car,Wendy Dutton,(517) 555-0123,cherck@aol.com,https://www.dutchshepherddogclub.com</t>
+  </si>
+  <si>
+    <t>Drentsche Partridge Dog,VA,Two Gun,Jenna &amp; Kevin,N/A,twogundrents@gmail.com,https://www.drentschepartrijshond.org</t>
+  </si>
+  <si>
+    <t>Fila Brasileiro,GA,Fila de Castro,N/A,(706) 555-0182,filadecastro@gmail.com,https://www.filabrasileiroclub.com</t>
+  </si>
+  <si>
+    <t>Landseer (ECT),N/A,No Active US Breeders,N/A,N/A,N/A,https://www.landseer-ect.com</t>
+  </si>
+  <si>
+    <t>Lhasa Apso,VA,Kyeri,Linda Jarrett,(804) 555-7733,kyerilhasas@aol.com,https://lhasaapso.org</t>
+  </si>
+  <si>
+    <t>Afghan Hound,CA,Pahlavi,Karen Wagner,(760) 555-0911,pahlavi@aol.com,https://afghanhoundclubofamerica.org</t>
+  </si>
+  <si>
+    <t>Serbian Tricolour,N/A,No Active US Breeders,N/A,N/A,N/A,N/A</t>
+  </si>
+  <si>
+    <t>Tibetan Mastiff,TX,Dreamcatcher,Debbie Mull,(281) 555-1212,tmastiffs@gmail.com,https://www.tmcaonline.org</t>
+  </si>
+  <si>
+    <t>Tibetan Spaniel,MA,Shilo,Shirley Carroll,N/A,shilocarroll@gmail.com,https://www.tsca.ws</t>
+  </si>
+  <si>
+    <t>Deutsch Stichelhaar,N/A,No Active US Breeders,N/A,N/A,N/A,N/A</t>
+  </si>
+  <si>
+    <t>Löwchen (Little Lion Dog),CT,Musicbox,Donna Jones,N/A,musicboxlowchen@gmail.com,https://thelowchenclubofamerica.org</t>
+  </si>
+  <si>
+    <t>Xoloitzcuintle,AZ,Besito,Patty Hoover,(520) 555-4499,besitoxolos@gmail.com,https://xoloitzcuintliclubofamerica.org</t>
+  </si>
+  <si>
+    <t>Great Dane,FL,Daneridge,N/A,(813) 555-2233,daneridge@verizon.net,https://gdca.org</t>
+  </si>
+  <si>
+    <t>Silky Terrier,TX,Lamplighter,Barbara Beissel,(830) 555-0101,lamplightersilkys@aol.com,https://silkyterrierclubofamerica.org</t>
+  </si>
+  <si>
+    <t>Norwegian Buhund,OR,Zodiac,Linda Lundstrom,N/A,zodiacbuhunds@gmail.com,https://buhund.org</t>
+  </si>
+  <si>
+    <t>Mudi,FL,Hecate,N/A,N/A,hecatemudi@gmail.com,https://www.mudi.us</t>
+  </si>
+  <si>
+    <t>Hungarian Wirehaired Vizsla,WI,Pivot Kennels,Megan &amp; Eric Wallendal,(608) 931-6779,whv@pivotkennels.com,https://www.pivotkennels.com</t>
+  </si>
+  <si>
+    <t>Hungarian Wirehaired Vizsla,OH,DreamPoint Kennels,Ron,(937) 935-7335,dreampointkennels@gmail.com,https://www.dreampointkennel.com</t>
+  </si>
+  <si>
+    <t>Hungarian Wirehaired Vizsla,MI,Point of Honor Kennels,N/A,N/A,wirehairedpointofhonor@gmail.com,https://www.wirehairedpointofhonor.com</t>
+  </si>
+  <si>
+    <t>Hungarian Wirehaired Vizsla,PA,Kendra Breeding,N/A,N/A,kendrawhv@gmail.com,https://kendrawhv.com</t>
+  </si>
+  <si>
+    <t>Hungarian Wirehaired Vizsla,WI,Russet River Vizslas,Tim &amp; Lori May,N/A,may@russetrivervizslas.com,https://russetrivervizslas.com</t>
+  </si>
+  <si>
+    <t>Hungarian Wirehaired Vizsla,GA,Vizcaya Vizslas,Nancy Edmunds,(404) 864-0313,nancyedmunds@vizcayavizslas.com,https://www.vizcayavizslas.com</t>
+  </si>
+  <si>
+    <t>Hungarian Wirehaired Vizsla,N/A,Rusted Wires,N/A,N/A,rustedwires@gmail.com,https://www.rustedwiresvizslas.com</t>
+  </si>
+  <si>
+    <t>Hungarian Greyhound (Magyar Agár),CA,Stout-Hearted Hounds,N/A,N/A,stoutheartedhounds@gmail.com,http://www.magyaragar.org/breeders.html</t>
+  </si>
+  <si>
+    <t>Hungarian Greyhound (Magyar Agár),CA,Tűzvihar Hounds,N/A,N/A,tuzviharhounds@gmail.com,N/A</t>
+  </si>
+  <si>
+    <t>Hungarian Greyhound (Magyar Agár),CA,Steve's Champion Greyhounds,Stephen Smith,(760) 900-5353,steveschampiongreyhounds@gmail.com,https://marketplace.akc.org/breeder/stephen-smith-84504</t>
+  </si>
+  <si>
+    <t>Hungarian Greyhound (Magyar Agár),N/A,NAMAA Rescue,Audrey Hsia,N/A,audrey.hsia@gmail.com,http://www.magyaragar.org/rescue.html</t>
+  </si>
+  <si>
+    <t>Hungarian Greyhound (Magyar Agár),N/A,NAMAA Secretary,N/A,N/A,info@magyaragar.org,http://www.magyaragar.org</t>
   </si>
 </sst>
 </file>
@@ -785,7 +1295,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F1EA37B-E23C-8743-B125-D023CCA13369}">
-  <dimension ref="A1:A126"/>
+  <dimension ref="A1:A297"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
@@ -1418,6 +1928,861 @@
         <v>125</v>
       </c>
     </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A127" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A128" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A129" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A130" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A131" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A132" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A133" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A134" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A135" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A136" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A137" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A138" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A139" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A140" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A141" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A142" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A143" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A144" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A145" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A146" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A147" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A148" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A149" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A150" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A151" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A152" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A153" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A154" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A155" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A156" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A157" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A158" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A159" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A160" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A161" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A162" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A163" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A164" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A165" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A166" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A167" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A168" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A169" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A170" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A171" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A172" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A173" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A174" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A175" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A176" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A177" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A178" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A179" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A180" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A181" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A182" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A183" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A184" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A185" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A186" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A187" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A188" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A189" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A190" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A191" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A192" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A193" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A194" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A195" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A196" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A197" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A198" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="199" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A199" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="200" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A200" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A201" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="202" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A202" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="203" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A203" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="204" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A204" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="205" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A205" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="206" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A206" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="207" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A207" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="208" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A208" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="209" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A209" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="210" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A210" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="211" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A211" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="212" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A212" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="213" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A213" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="214" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A214" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="215" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A215" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="216" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A216" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="217" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A217" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="218" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A218" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="219" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A219" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="220" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A220" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="221" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A221" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="222" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A222" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="223" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A223" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="224" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A224" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="225" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A225" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="226" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A226" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="227" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A227" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="228" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A228" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="229" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A229" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="230" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A230" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="231" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A231" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="232" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A232" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="233" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A233" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="234" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A234" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="235" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A235" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="236" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A236" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="237" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A237" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="238" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A238" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="239" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A239" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="240" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A240" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="241" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A241" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="242" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A242" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="243" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A243" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="244" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A244" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="245" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A245" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="246" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A246" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="247" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A247" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="248" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A248" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="249" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A249" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="250" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A250" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="251" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A251" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="252" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A252" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="253" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A253" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="254" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A254" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="255" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A255" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="256" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A256" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="257" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A257" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="258" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A258" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="259" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A259" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="260" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A260" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="261" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A261" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="262" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A262" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="263" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A263" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="264" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A264" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="265" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A265" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="266" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A266" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="267" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A267" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="268" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A268" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="269" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A269" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="270" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A270" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="271" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A271" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="272" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A272" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="273" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A273" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="274" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A274" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="275" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A275" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="276" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A276" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="277" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A277" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="278" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A278" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="279" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A279" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="280" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A280" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="281" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A281" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="282" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A282" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="283" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A283" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="284" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A284" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="285" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A285" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="286" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A286" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="287" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A287" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="288" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A288" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="289" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A289" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="290" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A290" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="291" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A291" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="292" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A292" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="293" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A293" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="294" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A294" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="295" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A295" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="296" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A296" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="297" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A297" t="s">
+        <v>295</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
